--- a/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 8,67</t>
+          <t>-9,73; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 3,35</t>
+          <t>-15,76; 3,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 15,51</t>
+          <t>-6,76; 14,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -1,54</t>
+          <t>-12,92; -1,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 80,95</t>
+          <t>-49,12; 65,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,73; 30,8</t>
+          <t>-66,86; 33,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 147,96</t>
+          <t>-35,29; 154,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,25</t>
+          <t>-0,94; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,55</t>
+          <t>-2,22; 4,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,4</t>
+          <t>-2,23; 4,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,79</t>
+          <t>-3,48; 1,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 96,62</t>
+          <t>-12,96; 90,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 56,73</t>
+          <t>-20,54; 55,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 51,78</t>
+          <t>-20,48; 61,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 48,18</t>
+          <t>-49,52; 41,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 1,11</t>
+          <t>-7,88; 0,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 3,17</t>
+          <t>-4,53; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,06</t>
+          <t>-5,79; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 1,8</t>
+          <t>-7,53; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 28,83</t>
+          <t>-78,67; 30,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 126,6</t>
+          <t>-68,61; 163,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,16; 68,4</t>
+          <t>-61,59; 64,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 47,47</t>
+          <t>-70,44; 45,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,07</t>
+          <t>-1,93; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,35</t>
+          <t>-2,58; 2,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,39</t>
+          <t>-1,68; 3,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,47</t>
+          <t>-3,96; 0,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 47,26</t>
+          <t>-21,59; 44,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 29,22</t>
+          <t>-23,83; 33,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 40,05</t>
+          <t>-15,82; 41,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 10,54</t>
+          <t>-53,74; 9,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 7,8</t>
+          <t>-10,36; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 3,7</t>
+          <t>-13,78; 3,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 14,97</t>
+          <t>-7,19; 14,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -1,52</t>
+          <t>-12,87; -1,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 65,11</t>
+          <t>-52,72; 70,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 33,26</t>
+          <t>-63,66; 32,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 154,12</t>
+          <t>-40,26; 153,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,25</t>
+          <t>-1,31; 4,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,4</t>
+          <t>-2,2; 4,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,97</t>
+          <t>-2,38; 4,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,67</t>
+          <t>-3,8; 1,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 90,16</t>
+          <t>-15,97; 88,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 55,47</t>
+          <t>-20,47; 57,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 61,19</t>
+          <t>-20,61; 53,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 41,25</t>
+          <t>-51,91; 31,1</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,74</t>
+          <t>-7,61; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,11</t>
+          <t>-4,93; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,28</t>
+          <t>-5,86; 3,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,9</t>
+          <t>-8,0; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,67; 30,31</t>
+          <t>-76,81; 36,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 163,25</t>
+          <t>-68,12; 129,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 64,63</t>
+          <t>-57,4; 69,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,44; 45,76</t>
+          <t>-73,9; 39,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,9</t>
+          <t>-2,05; 2,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,85</t>
+          <t>-2,87; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,52</t>
+          <t>-1,77; 3,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,42</t>
+          <t>-3,92; 0,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 44,41</t>
+          <t>-22,82; 39,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 33,82</t>
+          <t>-25,77; 33,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 41,19</t>
+          <t>-16,08; 39,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 9,84</t>
+          <t>-53,22; 9,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,94</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 7,6</t>
+          <t>-9,51; 8,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 3,49</t>
+          <t>-14,53; 3,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 14,73</t>
+          <t>-6,74; 15,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -1,54</t>
+          <t>-13,72; -1,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 70,84</t>
+          <t>-46,86; 80,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,66; 32,14</t>
+          <t>-63,73; 30,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 153,83</t>
+          <t>-36,28; 147,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,39%</t>
+          <t>-10,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,93</t>
+          <t>-1,28; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,66</t>
+          <t>-2,12; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,57</t>
+          <t>-2,36; 4,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,25</t>
+          <t>-3,27; 2,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 88,06</t>
+          <t>-15,47; 96,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 57,17</t>
+          <t>-19,05; 56,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 53,78</t>
+          <t>-20,6; 51,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,91; 31,1</t>
+          <t>-46,92; 51,31</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-35,45%</t>
+          <t>-40,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,17</t>
+          <t>-7,42; 1,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 2,83</t>
+          <t>-5,05; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 3,15</t>
+          <t>-5,97; 3,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 1,63</t>
+          <t>-8,07; 1,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,81; 36,69</t>
+          <t>-78,3; 28,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 129,29</t>
+          <t>-72,25; 126,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 69,93</t>
+          <t>-61,16; 68,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,9; 39,25</t>
+          <t>-71,95; 41,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,37%</t>
+          <t>-25,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,78</t>
+          <t>-1,66; 3,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,68</t>
+          <t>-2,57; 2,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,35</t>
+          <t>-1,81; 3,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,43</t>
+          <t>-3,93; 0,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 39,96</t>
+          <t>-18,45; 47,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 33,1</t>
+          <t>-24,12; 29,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 39,56</t>
+          <t>-16,83; 40,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 9,5</t>
+          <t>-52,2; 11,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-30,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.7184452424761373</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-5.111847533970251</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.736322958534549</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.322667745239338</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.04538566924259073</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3023891197474236</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2556784212102687</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,51; 8,67</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,53; 3,35</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 15,51</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,72; -1,67</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-46,86; 80,95</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-63,73; 30,8</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-36,28; 147,96</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.505805538449112</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-14.53482883728172</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.739567802244652</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.72112371691589</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4685896325382108</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6373171773782754</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3628452942634648</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.670293208896974</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.353655530633289</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>15.51062174307386</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-1.671817345101915</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.8095202957063933</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3080498300754754</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.479619584212117</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-10,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 5,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,12; 4,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 4,4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 2,07</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-15,47; 96,62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-19,05; 56,73</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,6; 51,78</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-46,92; 51,31</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.964831735041665</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.115488577629489</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.241550732700984</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.592905391960842</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2818840377520299</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1148988755224813</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1256666121738677</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1046338073426959</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-46,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-14,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-16,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-40,39%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.281858277654382</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.115315335897737</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.355304701270153</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.268113823165063</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1546690518713674</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1904523803040827</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2059938709895639</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4692311130201797</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,42; 1,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,05; 3,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 3,06</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,07; 1,23</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-78,3; 28,83</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-72,25; 126,6</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-61,16; 68,4</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-71,95; 41,92</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.252749259627923</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.547558742311645</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.399024131908519</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.069389618824133</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.9661822368206469</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5672990765343718</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5177597414295027</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5131149849197644</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-25,43%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.169996753288266</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.6587477067677782</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.221547525271045</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.186695417309509</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4655418184192572</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1439465843497556</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1672313678261445</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.4038740990217863</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 3,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 2,35</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 3,39</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,93; 0,58</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-18,45; 47,26</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,12; 29,22</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-16,83; 40,05</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-52,2; 11,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.423997066100626</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.047069545301854</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.972118097982553</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.069362164940523</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.783005450735431</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7225415676362836</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.611581367589777</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7194566590055694</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.110643599892235</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.166384888811059</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.062230712141111</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.231979365303689</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.28830203696038</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.266039989262629</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.6840219074059233</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4192276293284967</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4493245600126414</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.09104310207462274</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.787220284522247</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.5714892784457</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.05622515267998515</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.00966536954470457</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.08104671430221705</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2542724803351654</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.659884011802897</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.572967745917499</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.812628028949577</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.925839936393891</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1845428621367805</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2412401907283811</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1682623284933286</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5220405933438911</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.074829263049638</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.346883937287324</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.393424939764511</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.5791915486834485</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4726220245316389</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2921631965149846</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.400546664399573</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1132902671349751</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
